--- a/data/results/predictions_2025_all_models_with_n_pm_2025.xlsx
+++ b/data/results/predictions_2025_all_models_with_n_pm_2025.xlsx
@@ -1573,7 +1573,7 @@
         <v>0.4083389961667553</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4518996432921961</v>
+        <v>0.4518996432921963</v>
       </c>
       <c r="AA12" t="n">
         <v>0.3465983539059778</v>
@@ -1665,7 +1665,7 @@
         <v>0.322150101351609</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.628069217836969</v>
+        <v>1.628069217836968</v>
       </c>
       <c r="AA13" t="n">
         <v>1.746352239712419</v>
@@ -1941,7 +1941,7 @@
         <v>0.3375670713282506</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3025958371938966</v>
+        <v>0.3025958371938967</v>
       </c>
       <c r="AA16" t="n">
         <v>0.1602292754400629</v>
@@ -2309,7 +2309,7 @@
         <v>0.0817186292964901</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3574574098393837</v>
+        <v>0.3574574098393836</v>
       </c>
       <c r="AA20" t="n">
         <v>0.2973893756866849</v>
@@ -2401,7 +2401,7 @@
         <v>0.5240093760089105</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.9897506968886854</v>
+        <v>0.9897506968886853</v>
       </c>
       <c r="AA21" t="n">
         <v>0.597309060882465</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2516151070992835</v>
+        <v>0.2516151070992834</v>
       </c>
       <c r="AA23" t="n">
         <v>0.2813828041131907</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.1621182081205489</v>
+        <v>0.1621182081205488</v>
       </c>
       <c r="AA24" t="n">
         <v>0.241483064966427</v>
@@ -2863,7 +2863,7 @@
         <v>0.51840248615724</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.7313392604033555</v>
+        <v>0.7313392604033554</v>
       </c>
       <c r="AA26" t="n">
         <v>0.9778697252634824</v>
@@ -3140,7 +3140,7 @@
         <v>0.06286708542555236</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2924051517847328</v>
+        <v>0.2924051517847326</v>
       </c>
       <c r="AA29" t="n">
         <v>0.2335416284659564</v>
@@ -3692,7 +3692,7 @@
         <v>1.110042476458525</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.9144903934393898</v>
+        <v>0.9144903934393899</v>
       </c>
       <c r="AA35" t="n">
         <v>0.4558067539373578</v>
@@ -3876,7 +3876,7 @@
         <v>0.1527384036386698</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.09386388924025851</v>
+        <v>0.0938638892402585</v>
       </c>
       <c r="AA37" t="n">
         <v>0.09419155909548772</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.1624984409759251</v>
+        <v>0.162498440975925</v>
       </c>
       <c r="AA39" t="n">
         <v>0.1460224792229973</v>
@@ -4152,7 +4152,7 @@
         <v>0.1184489749262798</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.09267858182794748</v>
+        <v>0.09267858182794747</v>
       </c>
       <c r="AA40" t="n">
         <v>0.2027358404252795</v>
@@ -4244,7 +4244,7 @@
         <v>0.1184489749262798</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.09267858182794748</v>
+        <v>0.09267858182794747</v>
       </c>
       <c r="AA41" t="n">
         <v>0.2027358404252795</v>
@@ -4336,7 +4336,7 @@
         <v>0.2914530117660564</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.3967223898846517</v>
+        <v>0.3967223898846518</v>
       </c>
       <c r="AA42" t="n">
         <v>0.3862156218237958</v>
@@ -4612,7 +4612,7 @@
         <v>0.1856888987677929</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.1977563995042144</v>
+        <v>0.1977563995042145</v>
       </c>
       <c r="AA45" t="n">
         <v>0.3355645774173374</v>
@@ -5532,7 +5532,7 @@
         <v>0.08296568068329485</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.04099696759531981</v>
+        <v>0.04099696759531982</v>
       </c>
       <c r="AA55" t="n">
         <v>0.08365643222110092</v>
@@ -6268,7 +6268,7 @@
         <v>0.291604280476669</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.483925404331207</v>
+        <v>0.4839254043312071</v>
       </c>
       <c r="AA63" t="n">
         <v>0.3601253461693635</v>
@@ -6820,7 +6820,7 @@
         <v>0.5156820542417571</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.1907977427046527</v>
+        <v>0.1907977427046526</v>
       </c>
       <c r="AA69" t="n">
         <v>0.2615832959779711</v>
@@ -7004,7 +7004,7 @@
         <v>1.771422519027422</v>
       </c>
       <c r="Z71" t="n">
-        <v>3.257566693124072</v>
+        <v>3.257566693124071</v>
       </c>
       <c r="AA71" t="n">
         <v>2.582084654829428</v>
@@ -8292,7 +8292,7 @@
         <v>0.08440619928828968</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.04651049909487494</v>
+        <v>0.04651049909487495</v>
       </c>
       <c r="AA85" t="n">
         <v>0.04240784043687944</v>
@@ -8568,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.03089918507443756</v>
+        <v>0.03089918507443757</v>
       </c>
       <c r="AA88" t="n">
         <v>0.04652610242674303</v>
@@ -8752,7 +8752,7 @@
         <v>0.07489509402954736</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.09038290226760327</v>
+        <v>0.09038290226760326</v>
       </c>
       <c r="AA90" t="n">
         <v>0.1536274598401464</v>
@@ -9028,7 +9028,7 @@
         <v>0.08787423625503737</v>
       </c>
       <c r="Z93" t="n">
-        <v>0.06551458686106991</v>
+        <v>0.0655145868610699</v>
       </c>
       <c r="AA93" t="n">
         <v>0.04652610242674303</v>
@@ -9120,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA94" t="n">
         <v>0.04839631161908282</v>
@@ -9212,7 +9212,7 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA95" t="n">
         <v>0.04839631161908282</v>
@@ -9304,7 +9304,7 @@
         <v>0.02921454544914776</v>
       </c>
       <c r="Z96" t="n">
-        <v>0.08113622718405367</v>
+        <v>0.08113622718405365</v>
       </c>
       <c r="AA96" t="n">
         <v>0.09008780582267772</v>
@@ -9396,7 +9396,7 @@
         <v>0.03065506405414253</v>
       </c>
       <c r="Z97" t="n">
-        <v>0.09535133451763254</v>
+        <v>0.09535133451763256</v>
       </c>
       <c r="AA97" t="n">
         <v>0.1354716697730992</v>
@@ -9488,7 +9488,7 @@
         <v>0.3565212907724208</v>
       </c>
       <c r="Z98" t="n">
-        <v>0.06447105072285329</v>
+        <v>0.06447105072285331</v>
       </c>
       <c r="AA98" t="n">
         <v>0.1263671711728773</v>
@@ -9580,7 +9580,7 @@
         <v>0.3565212907724208</v>
       </c>
       <c r="Z99" t="n">
-        <v>0.06447105072285329</v>
+        <v>0.06447105072285331</v>
       </c>
       <c r="AA99" t="n">
         <v>0.1263671711728773</v>
@@ -9764,7 +9764,7 @@
         <v>0.3907646195208626</v>
       </c>
       <c r="Z101" t="n">
-        <v>0.2392271886334304</v>
+        <v>0.2392271886334303</v>
       </c>
       <c r="AA101" t="n">
         <v>0.3899741476251199</v>
@@ -9948,7 +9948,7 @@
         <v>0.08469969916666881</v>
       </c>
       <c r="Z103" t="n">
-        <v>0.04512981201016617</v>
+        <v>0.04512981201016619</v>
       </c>
       <c r="AA103" t="n">
         <v>0.08777469421096452</v>
@@ -10040,7 +10040,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z104" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA104" t="n">
         <v>0.04756872505273846</v>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA106" t="n">
         <v>0.04839631161908282</v>
@@ -10316,7 +10316,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z107" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA107" t="n">
         <v>0.04756872505273846</v>
@@ -10408,7 +10408,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z108" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA108" t="n">
         <v>0.04756872505273846</v>
@@ -10868,7 +10868,7 @@
         <v>0.3516127352006783</v>
       </c>
       <c r="Z113" t="n">
-        <v>0.07867238633196715</v>
+        <v>0.07867238633196713</v>
       </c>
       <c r="AA113" t="n">
         <v>0.1222489091830135</v>
@@ -11144,7 +11144,7 @@
         <v>0.3852918737526619</v>
       </c>
       <c r="Z116" t="n">
-        <v>0.9788966232614135</v>
+        <v>0.9788966232614136</v>
       </c>
       <c r="AA116" t="n">
         <v>0.8192118431777171</v>
@@ -11236,7 +11236,7 @@
         <v>1.330032948614527</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.292021738166569</v>
+        <v>1.292021738166568</v>
       </c>
       <c r="AA117" t="n">
         <v>0.03573073947480116</v>
@@ -11328,7 +11328,7 @@
         <v>0.004720822473115449</v>
       </c>
       <c r="Z118" t="n">
-        <v>0.4128612939502298</v>
+        <v>0.4128612939502299</v>
       </c>
       <c r="AA118" t="n">
         <v>0.3507883378308808</v>
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA120" t="n">
         <v>0.04839631161908282</v>
@@ -11604,7 +11604,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z121" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA121" t="n">
         <v>0.04756872505273846</v>
@@ -11698,7 +11698,7 @@
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA122" t="n">
         <v>0.04839631161908282</v>
